--- a/Day 1 Power Apps/Request-Sample-Data.xlsx
+++ b/Day 1 Power Apps/Request-Sample-Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsoftapc-my.sharepoint.com/personal/v-shtoo_microsoft_com/Documents/Power Platform Training/PP-Foundation-Bootcamp-main/Day 1 Power Apps/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sing Kwang Eng\Desktop\PP Foundation\Day 1 Power Apps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_77AD93DB2927FD753C272A7CCACB206B6590FABD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FEC489C-05E3-40B8-839D-967EBF1D58C4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198FC642-AA3F-41D5-B603-988ED8928A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,7 @@
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
     <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="40.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="45.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -515,7 +515,7 @@
         <v>45778</v>
       </c>
       <c r="C2" s="1">
-        <v>45780</v>
+        <v>46145</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -541,7 +541,7 @@
         <v>45779</v>
       </c>
       <c r="C3" s="1">
-        <v>45781</v>
+        <v>46146</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -567,7 +567,7 @@
         <v>45782</v>
       </c>
       <c r="C4" s="1">
-        <v>45782</v>
+        <v>46147</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -593,7 +593,7 @@
         <v>45783</v>
       </c>
       <c r="C5" s="1">
-        <v>45787</v>
+        <v>46152</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -619,7 +619,7 @@
         <v>45784</v>
       </c>
       <c r="C6" s="1">
-        <v>45784</v>
+        <v>46149</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -646,6 +646,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="baaaf2c8-0321-4768-8581-668a68072ce1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007F9AB11DF8DA5346820872D9420E39F7" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9917a6409e4da7f66f4733fc2e541b31">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="baaaf2c8-0321-4768-8581-668a68072ce1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c6c3d77ff06a11e6079a5a4f231af011" ns1:_="" ns2:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -858,37 +879,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="baaaf2c8-0321-4768-8581-668a68072ce1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52315537-5FF8-464B-B61A-5ECE8EE3B54F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D24BAE8-5AE2-42E0-9942-5C448D90685A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="baaaf2c8-0321-4768-8581-668a68072ce1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{528275E0-B90E-477B-94F8-5110445476B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{528275E0-B90E-477B-94F8-5110445476B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D24BAE8-5AE2-42E0-9942-5C448D90685A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52315537-5FF8-464B-B61A-5ECE8EE3B54F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="baaaf2c8-0321-4768-8581-668a68072ce1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Day 1 Power Apps/Request-Sample-Data.xlsx
+++ b/Day 1 Power Apps/Request-Sample-Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sing Kwang Eng\Desktop\PP Foundation\Day 1 Power Apps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198FC642-AA3F-41D5-B603-988ED8928A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFFB2CC-4255-47DD-8458-97F060A73B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -512,7 +512,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="1">
-        <v>45778</v>
+        <v>46143</v>
       </c>
       <c r="C2" s="1">
         <v>46145</v>
@@ -538,7 +538,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="1">
-        <v>45779</v>
+        <v>46144</v>
       </c>
       <c r="C3" s="1">
         <v>46146</v>
@@ -564,7 +564,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="1">
-        <v>45782</v>
+        <v>46147</v>
       </c>
       <c r="C4" s="1">
         <v>46147</v>
@@ -590,7 +590,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="1">
-        <v>45783</v>
+        <v>46148</v>
       </c>
       <c r="C5" s="1">
         <v>46152</v>
@@ -616,7 +616,7 @@
         <v>27</v>
       </c>
       <c r="B6" s="1">
-        <v>45784</v>
+        <v>46149</v>
       </c>
       <c r="C6" s="1">
         <v>46149</v>
@@ -646,27 +646,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="baaaf2c8-0321-4768-8581-668a68072ce1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007F9AB11DF8DA5346820872D9420E39F7" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9917a6409e4da7f66f4733fc2e541b31">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="baaaf2c8-0321-4768-8581-668a68072ce1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c6c3d77ff06a11e6079a5a4f231af011" ns1:_="" ns2:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -879,26 +858,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="baaaf2c8-0321-4768-8581-668a68072ce1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D24BAE8-5AE2-42E0-9942-5C448D90685A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="baaaf2c8-0321-4768-8581-668a68072ce1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{528275E0-B90E-477B-94F8-5110445476B2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52315537-5FF8-464B-B61A-5ECE8EE3B54F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -917,6 +898,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{528275E0-B90E-477B-94F8-5110445476B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D24BAE8-5AE2-42E0-9942-5C448D90685A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="baaaf2c8-0321-4768-8581-668a68072ce1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{87867195-f2b8-4ac2-b0b6-6bb73cb33afc}" enabled="1" method="Privileged" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" removed="0"/>
